--- a/data/WP17/WP17_sachgebiete_fraktionslos.xlsx
+++ b/data/WP17/WP17_sachgebiete_fraktionslos.xlsx
@@ -685,7 +685,7 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>29.3333333333333</v>
+        <v>29.9230769230769</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
@@ -2506,13 +2506,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DFC4E5F-04AC-4401-98F2-43F31782ACD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0CCA48D-45CC-4715-8D29-B47B4037B468}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD59DF3-3689-43B9-9083-BADC0F3BB850}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{165CE9FB-610A-4094-A765-A61A55F779F7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2B176E-014D-4270-8971-856F0854A25E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C0924E-098E-4B53-875B-694F7F04CBA7}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_fraktionslos.xlsx
+++ b/data/WP17/WP17_sachgebiete_fraktionslos.xlsx
@@ -446,7 +446,7 @@
         <v>31.734693877551</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>29.5384615384615</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         <v>32.7941176470588</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         <v>28.6666666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>29.04</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>29.8095238095238</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -582,7 +582,7 @@
         <v>31.0714285714286</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -684,7 +684,7 @@
         <v>37.8888888888889</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -701,7 +701,7 @@
         <v>28.5</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -735,7 +735,7 @@
         <v>31.75</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -752,7 +752,7 @@
         <v>27.625</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -769,7 +769,7 @@
         <v>30.7142857142857</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1006,13 +1006,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F80ABD-A14C-45FA-A6FE-46434CF78E81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{931DBFE5-DF26-48BD-8B92-61FEE46DF969}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F2C53A6-F37E-492F-98E7-E2CAC1A1EC9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18EA68EF-CC91-45EF-84D6-CB3C27A6C647}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83C54E3C-3E6A-4DAF-B2A6-86CBC8C6DA50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD03BBC7-9B4E-499D-825F-9AA5BD0FB131}"/>
 </file>